--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T13:03:45+00:00</t>
+    <t>2026-01-12T10:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:11:28+00:00</t>
+    <t>2026-01-12T10:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:18:34+00:00</t>
+    <t>2026-01-12T10:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:26:55+00:00</t>
+    <t>2026-01-28T07:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:37:37+00:00</t>
+    <t>2026-01-28T07:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:43:18+00:00</t>
+    <t>2026-01-28T07:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:44:30+00:00</t>
+    <t>2026-01-28T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:46:49+00:00</t>
+    <t>2026-02-24T18:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T18:21:42+00:00</t>
+    <t>2026-02-26T08:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:55:53+00:00</t>
+    <t>2026-03-06T07:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T07:38:40+00:00</t>
+    <t>2026-03-06T14:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:26:35+00:00</t>
+    <t>2026-03-09T09:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T09:58:26+00:00</t>
+    <t>2026-03-11T09:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T09:54:15+00:00</t>
+    <t>2026-03-18T07:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>element:Slot</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot#Slot</t>
   </si>
   <si>
     <t>ID</t>
@@ -470,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -629,14 +626,6 @@
       </c>
       <c r="B20" t="s" s="2">
         <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -689,115 +678,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>73</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -813,22 +802,22 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -888,16 +877,16 @@
         <v>28</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AI2" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>18</v>
@@ -905,10 +894,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -916,28 +905,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -988,30 +977,30 @@
         <v>18</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AG3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="s" s="2">
+      <c r="AJ3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK3" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="AJ3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1019,10 +1008,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>18</v>
@@ -1034,13 +1023,13 @@
         <v>18</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1079,31 +1068,31 @@
         <v>18</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AF4" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="AG4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH4" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH4" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AI4" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>18</v>
@@ -1111,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1122,10 +1111,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>18</v>
@@ -1137,16 +1126,16 @@
         <v>18</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1196,13 +1185,13 @@
         <v>18</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>18</v>
@@ -1211,15 +1200,15 @@
         <v>18</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1227,10 +1216,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>18</v>
@@ -1242,13 +1231,13 @@
         <v>18</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L6" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1299,22 +1288,22 @@
         <v>18</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="AK6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T07:58:35+00:00</t>
+    <t>2026-04-07T11:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:55:37+00:00</t>
+    <t>2026-04-08T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:25+00:00</t>
+    <t>2026-06-09T13:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:05:25+00:00</t>
+    <t>2026-06-09T13:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:21+00:00</t>
+    <t>2026-06-09T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:55:01+00:00</t>
+    <t>2026-06-10T09:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-booking-url</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-booking-url</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:07:46+00:00</t>
+    <t>2026-08-18T08:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:43:24+00:00</t>
+    <t>2026-08-18T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:20:27+00:00</t>
+    <t>2026-08-31T14:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-appointment-booking-url.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:45:12+00:00</t>
+    <t>2026-09-01T07:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
